--- a/real_estate_forms/010_vacant_land_listing_survey--real_estate_forms.xlsx
+++ b/real_estate_forms/010_vacant_land_listing_survey--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'vacant'}</t>
+          <t>vacant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Vacant'}</t>
+          <t>Vacant</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'leased'}</t>
+          <t>leased</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Leased'}</t>
+          <t>Leased</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Sold'}</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'r-1'}</t>
+          <t>r-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'R-1'}</t>
+          <t>R-1</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'r-2'}</t>
+          <t>r-2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'R-2'}</t>
+          <t>R-2</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'r-3'}</t>
+          <t>r-3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'R-3'}</t>
+          <t>R-3</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'agricultural'}</t>
+          <t>agricultural</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Agricultural'}</t>
+          <t>Agricultural</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'conservation'}</t>
+          <t>conservation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Conservation'}</t>
+          <t>Conservation</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'recreation'}</t>
+          <t>recreation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Recreation'}</t>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'single_family_residence'}</t>
+          <t>single_family_residence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Single Family Residence'}</t>
+          <t>Single Family Residence</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'multi_family_residence'}</t>
+          <t>multi_family_residence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Multi Family Residence'}</t>
+          <t>Multi Family Residence</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'commercial_building'}</t>
+          <t>commercial_building</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Commercial Building'}</t>
+          <t>Commercial Building</t>
         </is>
       </c>
     </row>
